--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>16.59093</v>
+      </c>
+      <c r="D2" t="n">
         <v>16.45183</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>16.52375</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16.59093</v>
       </c>
       <c r="F2" t="n">
         <v>42.52035</v>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.33441</v>
+        <v>16.64004</v>
       </c>
       <c r="D3" t="n">
         <v>16.23943</v>
       </c>
       <c r="E3" t="n">
-        <v>16.64004</v>
+        <v>16.33441</v>
       </c>
       <c r="F3" t="n">
         <v>42.15687</v>
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16.80565</v>
+      </c>
+      <c r="D4" t="n">
         <v>16.71835</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>16.71962</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.80565</v>
       </c>
       <c r="F4" t="n">
         <v>41.70683</v>
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.71784</v>
+        <v>16.75309</v>
       </c>
       <c r="D7" t="n">
         <v>15.97461</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75309</v>
+        <v>16.71784</v>
       </c>
       <c r="F7" t="n">
         <v>21.46976</v>
